--- a/backend/data/financials_by_company/1490.HK.xlsx
+++ b/backend/data/financials_by_company/1490.HK.xlsx
@@ -4191,10 +4191,8 @@
           <t>Beijing</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>100015</t>
-        </is>
+      <c r="D2" t="n">
+        <v>100015</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4400,7 +4398,7 @@
         <v>-3457000</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
         <v>-1.294</v>
@@ -4617,7 +4615,7 @@
         <v>37.837837</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT2" t="n">
         <v>-0.0016199946</v>
